--- a/四足-夏元瑞-5套/四足-夏元瑞-5套.xlsx
+++ b/四足-夏元瑞-5套/四足-夏元瑞-5套.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1117,19 +1117,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>208280</xdr:colOff>
+      <xdr:colOff>114300</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>109220</xdr:rowOff>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2912745</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>2015490</xdr:rowOff>
+      <xdr:colOff>2873375</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 1"/>
+        <xdr:cNvPr id="7" name="图片 6"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1142,8 +1142,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2608580" y="1480820"/>
-          <a:ext cx="2704465" cy="1906270"/>
+          <a:off x="2514600" y="1419225"/>
+          <a:ext cx="2759075" cy="2047875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1159,19 +1159,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>222885</xdr:colOff>
+      <xdr:colOff>114300</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>62865</xdr:rowOff>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2924175</xdr:colOff>
+      <xdr:colOff>2825750</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>2085975</xdr:rowOff>
+      <xdr:rowOff>2071370</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2"/>
+        <xdr:cNvPr id="19" name="图片 18"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1184,8 +1184,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2623185" y="3529965"/>
-          <a:ext cx="2701290" cy="2023110"/>
+          <a:off x="2514600" y="3495675"/>
+          <a:ext cx="2711450" cy="2042795"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1201,19 +1201,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>247650</xdr:colOff>
+      <xdr:colOff>95250</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2862580</xdr:colOff>
+      <xdr:colOff>2828925</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>2048510</xdr:rowOff>
+      <xdr:rowOff>2076450</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="图片 3"/>
+        <xdr:cNvPr id="20" name="图片 19"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1226,8 +1226,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2647950" y="5629275"/>
-          <a:ext cx="2614930" cy="1981835"/>
+          <a:off x="2495550" y="5591175"/>
+          <a:ext cx="2733675" cy="2047875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1243,19 +1243,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>272415</xdr:colOff>
+      <xdr:colOff>76200</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>36830</xdr:rowOff>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2901950</xdr:colOff>
+      <xdr:colOff>2827020</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>2012315</xdr:rowOff>
+      <xdr:rowOff>2089150</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="图片 4"/>
+        <xdr:cNvPr id="23" name="图片 22"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1268,8 +1268,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2672715" y="7694930"/>
-          <a:ext cx="2629535" cy="1975485"/>
+          <a:off x="2476500" y="7667625"/>
+          <a:ext cx="2750820" cy="2079625"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1285,19 +1285,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>230505</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>113030</xdr:rowOff>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2867025</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:colOff>2813050</xdr:colOff>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>2085975</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="图片 5"/>
+        <xdr:cNvPr id="25" name="图片 24"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1310,8 +1310,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2630805" y="9866630"/>
-          <a:ext cx="2636520" cy="1972945"/>
+          <a:off x="2457450" y="11877675"/>
+          <a:ext cx="2755900" cy="2057400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1327,19 +1327,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>231775</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2840990</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>2051050</xdr:rowOff>
+      <xdr:colOff>2843530</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>2072005</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="图片 7"/>
+        <xdr:cNvPr id="29" name="图片 28"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1352,8 +1352,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2632075" y="11944350"/>
-          <a:ext cx="2609215" cy="1955800"/>
+          <a:off x="2533650" y="20250150"/>
+          <a:ext cx="2710180" cy="2052955"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1369,19 +1369,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>112395</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2854325</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>2070100</xdr:rowOff>
+      <xdr:colOff>2823210</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>2066290</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="图片 8"/>
+        <xdr:cNvPr id="31" name="图片 30"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1394,8 +1394,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2512695" y="16068675"/>
-          <a:ext cx="2741930" cy="2041525"/>
+          <a:off x="2476500" y="24441150"/>
+          <a:ext cx="2747010" cy="2047240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1411,19 +1411,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>111760</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2835910</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>2066925</xdr:rowOff>
+      <xdr:colOff>2754630</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>2058035</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="图片 13"/>
+        <xdr:cNvPr id="2" name="图片 1"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1436,8 +1436,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2512060" y="18145125"/>
-          <a:ext cx="2724150" cy="2057400"/>
+          <a:off x="2476500" y="9810750"/>
+          <a:ext cx="2678430" cy="2000885"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1453,19 +1453,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>127635</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2842895</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>2077085</xdr:rowOff>
+      <xdr:colOff>2843530</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>2077720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="图片 15"/>
+        <xdr:cNvPr id="3" name="图片 2"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1478,8 +1478,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2527935" y="20250150"/>
-          <a:ext cx="2715260" cy="2058035"/>
+          <a:off x="2495550" y="13963650"/>
+          <a:ext cx="2748280" cy="2058670"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1495,19 +1495,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2755900</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>2045970</xdr:rowOff>
+      <xdr:colOff>2831465</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>2085975</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="图片 9"/>
+        <xdr:cNvPr id="4" name="图片 3"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1520,8 +1520,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2590800" y="26641425"/>
-          <a:ext cx="2565400" cy="1922145"/>
+          <a:off x="2447925" y="16059150"/>
+          <a:ext cx="2783840" cy="2066925"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1537,19 +1537,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>20955</xdr:rowOff>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2470785</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>2037715</xdr:rowOff>
+      <xdr:colOff>2808605</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>2077720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="图片 10"/>
+        <xdr:cNvPr id="5" name="图片 4"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1562,8 +1562,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2638425" y="28634055"/>
-          <a:ext cx="2232660" cy="2016760"/>
+          <a:off x="2447925" y="18173700"/>
+          <a:ext cx="2760980" cy="2039620"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1579,19 +1579,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2786380</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>2038985</xdr:rowOff>
+      <xdr:colOff>2842260</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>2057400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="图片 16"/>
+        <xdr:cNvPr id="6" name="图片 5"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1604,8 +1604,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2543175" y="30765750"/>
-          <a:ext cx="2643505" cy="1981835"/>
+          <a:off x="2457450" y="22332950"/>
+          <a:ext cx="2785110" cy="2051050"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1621,19 +1621,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2816860</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>2058670</xdr:rowOff>
+      <xdr:colOff>2792095</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>2078990</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="图片 17"/>
+        <xdr:cNvPr id="8" name="图片 7"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1646,8 +1646,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2609850" y="14030325"/>
-          <a:ext cx="2607310" cy="1972945"/>
+          <a:off x="2457450" y="26527125"/>
+          <a:ext cx="2734945" cy="2069465"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1663,19 +1663,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:colOff>24765</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>18415</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2797175</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>2093595</xdr:rowOff>
+      <xdr:colOff>2746375</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>2082165</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="图片 20"/>
+        <xdr:cNvPr id="9" name="图片 8"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1688,8 +1688,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2419350" y="22355175"/>
-          <a:ext cx="2778125" cy="2065020"/>
+          <a:off x="2425065" y="28631515"/>
+          <a:ext cx="2721610" cy="2063750"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1705,19 +1705,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>38735</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2809875</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>2052320</xdr:rowOff>
+      <xdr:colOff>2787650</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>2083435</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="图片 21"/>
+        <xdr:cNvPr id="10" name="图片 9"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1730,8 +1730,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2495550" y="24498300"/>
-          <a:ext cx="2714625" cy="1976120"/>
+          <a:off x="2439035" y="30737175"/>
+          <a:ext cx="2748915" cy="2054860"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="B4" s="4">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>

--- a/四足-夏元瑞-5套/四足-夏元瑞-5套.xlsx
+++ b/四足-夏元瑞-5套/四足-夏元瑞-5套.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
   <si>
     <t>零件名称：</t>
   </si>
@@ -117,6 +117,9 @@
   </si>
   <si>
     <t>髋关节限位块</t>
+  </si>
+  <si>
+    <t>钣金快拆垫块</t>
   </si>
 </sst>
 </file>
@@ -129,7 +132,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -168,6 +171,13 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1" tint="0.05"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -711,152 +721,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -923,6 +933,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1621,48 +1643,6 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2792095</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>2078990</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="图片 7"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId13"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2457450" y="26527125"/>
-          <a:ext cx="2734945" cy="2069465"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
       <xdr:colOff>24765</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>18415</xdr:rowOff>
@@ -1681,7 +1661,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId14"/>
+        <a:blip r:embed="rId13"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1723,7 +1703,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId15"/>
+        <a:blip r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1732,6 +1712,90 @@
         <a:xfrm>
           <a:off x="2439035" y="30737175"/>
           <a:ext cx="2748915" cy="2054860"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2845435</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>2083435</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="图片 10"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2505075" y="26536650"/>
+          <a:ext cx="2740660" cy="2064385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>37465</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2783205</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>2068830</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="图片 13"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2457450" y="32841565"/>
+          <a:ext cx="2726055" cy="2031365"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2064,7 +2128,7 @@
       </c>
       <c r="B4" s="4">
         <f ca="1">TODAY()</f>
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -2118,19 +2182,19 @@
       <c r="H7" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="24"/>
-      <c r="Q7" s="24"/>
-      <c r="R7" s="24"/>
-      <c r="S7" s="24"/>
-      <c r="T7" s="24"/>
-      <c r="U7" s="24"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="28"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="28"/>
+      <c r="R7" s="28"/>
+      <c r="S7" s="28"/>
+      <c r="T7" s="28"/>
+      <c r="U7" s="28"/>
     </row>
     <row r="8" ht="13.5" spans="1:8">
       <c r="A8" s="1"/>
@@ -2436,7 +2500,25 @@
       </c>
       <c r="H23" s="8"/>
     </row>
-    <row r="24" ht="165" customHeight="1"/>
+    <row r="24" ht="165" customHeight="1" spans="2:8">
+      <c r="B24" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="25"/>
+      <c r="D24" s="26">
+        <v>4</v>
+      </c>
+      <c r="E24" s="26">
+        <v>5</v>
+      </c>
+      <c r="F24" s="26">
+        <v>20</v>
+      </c>
+      <c r="G24" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="25"/>
+    </row>
     <row r="25" ht="165" customHeight="1"/>
     <row r="26" ht="165" customHeight="1"/>
     <row r="27" ht="165" customHeight="1"/>
